--- a/supplier_risk_100_platform_ready.xlsx
+++ b/supplier_risk_100_platform_ready.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Risk Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +36,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,16 +56,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F4FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,15 +101,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -498,14 +478,13 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -546,45 +525,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>delivery_performance</t>
+          <t>on_time_delivery_pct</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>financial_stability</t>
+          <t>defect_rate_pct</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>lead_time_days</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>financial_health</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>compliance_score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>lead_time_days</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>defect_rate</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>on_time_delivery</t>
+          <t>dependency_score</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dependency_score</t>
+          <t>sub_tier_count</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>sub_tier_count</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
@@ -616,33 +590,30 @@
         <v>0.76</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.58</v>
+        <v>55.2</v>
       </c>
       <c r="I2" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="L2" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>1.66</v>
-      </c>
       <c r="M2" s="3" t="n">
-        <v>57.3</v>
+        <v>0.14</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -674,33 +645,30 @@
         <v>0.74</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>69</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.99</v>
+        <v>95</v>
       </c>
       <c r="I3" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>0.47</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>2.65</v>
-      </c>
       <c r="M3" s="5" t="n">
-        <v>100</v>
+        <v>0.21</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="O3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -732,33 +700,30 @@
         <v>0.76</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.84</v>
+        <v>86.8</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="M4" s="3" t="n">
-        <v>82.2</v>
+        <v>0.38</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -790,33 +755,30 @@
         <v>0.71</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I5" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>0.63</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>3.53</v>
-      </c>
       <c r="M5" s="5" t="n">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -848,33 +810,30 @@
         <v>0.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.58</v>
+        <v>58</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>98.5</v>
+        <v>0.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -906,33 +865,30 @@
         <v>0.73</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.9</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I7" s="5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>4.25</v>
-      </c>
       <c r="M7" s="5" t="n">
-        <v>88.59999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -964,33 +920,30 @@
         <v>0.65</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.95</v>
+        <v>95</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.64</v>
+        <v>62.3</v>
       </c>
       <c r="I8" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.47</v>
-      </c>
       <c r="M8" s="3" t="n">
-        <v>61.3</v>
+        <v>0.16</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1022,33 +975,30 @@
         <v>0.73</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.86</v>
+        <v>86</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.96</v>
+        <v>96.7</v>
       </c>
       <c r="I9" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>0.46</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="L9" s="5" t="n">
         <v>0.91</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>0.9</v>
-      </c>
       <c r="M9" s="5" t="n">
-        <v>98</v>
+        <v>0.28</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1080,33 +1030,30 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.97</v>
+        <v>97</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.64</v>
+        <v>63.8</v>
       </c>
       <c r="I10" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>0.87</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.48</v>
-      </c>
       <c r="M10" s="3" t="n">
-        <v>63.1</v>
+        <v>0.43</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1138,33 +1085,30 @@
         <v>0.89</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>0.96</v>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J11" s="5" t="n">
+      <c r="L11" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0.66</v>
-      </c>
       <c r="M11" s="5" t="n">
-        <v>91.09999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1196,33 +1140,30 @@
         <v>0.71</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.54</v>
+        <v>54</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.76</v>
+        <v>76.5</v>
       </c>
       <c r="I12" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="3" t="n">
         <v>0.61</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>3.96</v>
-      </c>
       <c r="M12" s="3" t="n">
-        <v>73.7</v>
+        <v>0.09</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1254,33 +1195,30 @@
         <v>0.75</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.49</v>
+        <v>50</v>
       </c>
       <c r="I13" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="L13" s="5" t="n">
         <v>0.83</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0.75</v>
-      </c>
       <c r="M13" s="5" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1312,33 +1250,30 @@
         <v>0.76</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>81</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.55</v>
+        <v>59.8</v>
       </c>
       <c r="I14" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="L14" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>2.17</v>
-      </c>
       <c r="M14" s="3" t="n">
-        <v>57.7</v>
+        <v>0.66</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1370,33 +1305,30 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>56</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.52</v>
+        <v>52.4</v>
       </c>
       <c r="I15" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>0.77</v>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>3.89</v>
-      </c>
       <c r="M15" s="5" t="n">
-        <v>53.7</v>
+        <v>0.12</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O15" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1428,33 +1360,30 @@
         <v>0.78</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.75</v>
+        <v>72</v>
       </c>
       <c r="I16" s="3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>3.17</v>
-      </c>
       <c r="M16" s="3" t="n">
-        <v>77.5</v>
+        <v>0.18</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1486,33 +1415,30 @@
         <v>0.79</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.67</v>
+        <v>70.7</v>
       </c>
       <c r="I17" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>1.59</v>
-      </c>
       <c r="M17" s="5" t="n">
-        <v>64.09999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1544,33 +1470,30 @@
         <v>0.71</v>
       </c>
       <c r="G18" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L18" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>1.63</v>
-      </c>
       <c r="M18" s="3" t="n">
-        <v>59.3</v>
+        <v>0.17</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="O18" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1602,33 +1525,30 @@
         <v>0.6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.85</v>
+        <v>85</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.58</v>
+        <v>55.5</v>
       </c>
       <c r="I19" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>0.31</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>0.92</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="M19" s="5" t="n">
-        <v>56.8</v>
+        <v>0.28</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1660,33 +1580,30 @@
         <v>0.77</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.76</v>
+        <v>76</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.52</v>
+        <v>52.7</v>
       </c>
       <c r="I20" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K20" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="L20" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>2.21</v>
-      </c>
       <c r="M20" s="3" t="n">
-        <v>50.7</v>
+        <v>0.32</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="O20" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1718,33 +1635,30 @@
         <v>0.63</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.68</v>
+        <v>69.2</v>
       </c>
       <c r="I21" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>2.63</v>
-      </c>
       <c r="M21" s="5" t="n">
-        <v>69.59999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1776,33 +1690,30 @@
         <v>0.74</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.6</v>
+        <v>60.6</v>
       </c>
       <c r="I22" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K22" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>1.07</v>
-      </c>
       <c r="M22" s="3" t="n">
-        <v>60.2</v>
+        <v>0.59</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="O22" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1834,33 +1745,30 @@
         <v>0.83</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.78</v>
+        <v>78</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.93</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I23" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.74</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>1.89</v>
-      </c>
       <c r="M23" s="5" t="n">
-        <v>91.59999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1892,33 +1800,30 @@
         <v>0.67</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.82</v>
+        <v>82.5</v>
       </c>
       <c r="I24" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K24" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="L24" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>3.16</v>
-      </c>
       <c r="M24" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="O24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="3" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1950,33 +1855,30 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.84</v>
+        <v>83</v>
       </c>
       <c r="I25" s="5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>0.71</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="L25" s="5" t="n">
         <v>0.61</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>2.28</v>
-      </c>
       <c r="M25" s="5" t="n">
-        <v>87.09999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2008,33 +1910,30 @@
         <v>0.87</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.74</v>
+        <v>74</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.95</v>
+        <v>97.5</v>
       </c>
       <c r="I26" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>2.44</v>
-      </c>
       <c r="M26" s="3" t="n">
-        <v>96</v>
+        <v>0.22</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2066,33 +1965,30 @@
         <v>0.82</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.58</v>
+        <v>58</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.78</v>
+        <v>77.2</v>
       </c>
       <c r="I27" s="5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>0.99</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="L27" s="5" t="n">
         <v>0.96</v>
       </c>
-      <c r="K27" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>3.59</v>
-      </c>
       <c r="M27" s="5" t="n">
-        <v>80</v>
+        <v>0.33</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2124,33 +2020,30 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>95.09999999999999</v>
-      </c>
       <c r="N28" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O28" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P28" s="3" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2182,33 +2075,30 @@
         <v>0.67</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>81</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.45</v>
+        <v>50</v>
       </c>
       <c r="I29" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="K29" s="5" t="n">
         <v>0.65</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="L29" s="5" t="n">
         <v>0.74</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>1.79</v>
-      </c>
       <c r="M29" s="5" t="n">
-        <v>50</v>
+        <v>0.25</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2240,33 +2130,30 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.89</v>
+        <v>89</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.65</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I30" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K30" s="3" t="n">
         <v>0.64</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="L30" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K30" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0.79</v>
-      </c>
       <c r="M30" s="3" t="n">
-        <v>61.6</v>
+        <v>0.44</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2298,33 +2185,30 @@
         <v>0.71</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>69</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.63</v>
+        <v>63.6</v>
       </c>
       <c r="I31" s="5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K31" s="5" t="n">
         <v>0.91</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="L31" s="5" t="n">
         <v>0.71</v>
       </c>
-      <c r="K31" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>2.71</v>
-      </c>
       <c r="M31" s="5" t="n">
-        <v>63.6</v>
+        <v>0.46</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2356,33 +2240,30 @@
         <v>0.64</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.46</v>
+        <v>50</v>
       </c>
       <c r="I32" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K32" s="3" t="n">
         <v>0.61</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="L32" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>1.68</v>
-      </c>
       <c r="M32" s="3" t="n">
-        <v>50</v>
+        <v>0.16</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="P32" s="3" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2414,33 +2295,30 @@
         <v>0.82</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.99</v>
+        <v>99</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0.53</v>
       </c>
       <c r="J33" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L33" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0.53</v>
-      </c>
       <c r="M33" s="5" t="n">
-        <v>99.8</v>
+        <v>0.23</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2472,33 +2350,30 @@
         <v>0.73</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.83</v>
+        <v>83</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.68</v>
+        <v>67</v>
       </c>
       <c r="I34" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K34" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="L34" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="M34" s="3" t="n">
-        <v>70</v>
+        <v>0.53</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="O34" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P34" s="3" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2530,33 +2405,30 @@
         <v>0.77</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>2.05</v>
-      </c>
       <c r="M35" s="5" t="n">
-        <v>91</v>
+        <v>0.41</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2588,33 +2460,30 @@
         <v>0.68</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.58</v>
+        <v>56.9</v>
       </c>
       <c r="I36" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>2.06</v>
-      </c>
       <c r="M36" s="3" t="n">
-        <v>57.8</v>
+        <v>0.12</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O36" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P36" s="3" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2646,33 +2515,30 @@
         <v>0.64</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.67</v>
+        <v>67</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.66</v>
+        <v>61.4</v>
       </c>
       <c r="I37" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K37" s="5" t="n">
         <v>0.54</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="L37" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>2.77</v>
-      </c>
       <c r="M37" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2704,33 +2570,30 @@
         <v>0.74</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.59</v>
+        <v>59</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.77</v>
+        <v>78.2</v>
       </c>
       <c r="I38" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K38" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="L38" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>3.58</v>
-      </c>
       <c r="M38" s="3" t="n">
-        <v>83.2</v>
+        <v>0.29</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2762,33 +2625,30 @@
         <v>0.63</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.85</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I39" s="5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K39" s="5" t="n">
         <v>0.51</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="L39" s="5" t="n">
         <v>0.68</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>3.08</v>
-      </c>
       <c r="M39" s="5" t="n">
-        <v>83.7</v>
+        <v>0.18</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O39" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2820,33 +2680,30 @@
         <v>0.8</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.66</v>
+        <v>69</v>
       </c>
       <c r="I40" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>1.69</v>
-      </c>
       <c r="M40" s="3" t="n">
-        <v>63.9</v>
+        <v>0.15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O40" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P40" s="3" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2878,33 +2735,30 @@
         <v>0.74</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.63</v>
+        <v>60.4</v>
       </c>
       <c r="I41" s="5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K41" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="L41" s="5" t="n">
         <v>0.96</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>1.82</v>
-      </c>
       <c r="M41" s="5" t="n">
-        <v>61.7</v>
+        <v>0.24</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O41" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2936,33 +2790,30 @@
         <v>0.88</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.9</v>
+        <v>90.8</v>
       </c>
       <c r="I42" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K42" s="3" t="n">
         <v>0.99</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>2.27</v>
-      </c>
       <c r="M42" s="3" t="n">
-        <v>90.5</v>
+        <v>0.26</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="O42" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P42" s="3" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2994,33 +2845,30 @@
         <v>0.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.66</v>
+        <v>64</v>
       </c>
       <c r="I43" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K43" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="L43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>3.94</v>
-      </c>
       <c r="M43" s="5" t="n">
-        <v>62.4</v>
+        <v>0.06</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O43" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3052,33 +2900,30 @@
         <v>0.76</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.83</v>
+        <v>83</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.89</v>
+        <v>87.7</v>
       </c>
       <c r="I44" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K44" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="L44" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="K44" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>1.46</v>
-      </c>
       <c r="M44" s="3" t="n">
-        <v>87.3</v>
+        <v>0.26</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="O44" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="3" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3110,33 +2955,30 @@
         <v>0.67</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.95</v>
+        <v>95</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.67</v>
+        <v>68.5</v>
       </c>
       <c r="I45" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K45" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="J45" s="5" t="n">
+      <c r="L45" s="5" t="n">
         <v>0.83</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>0.48</v>
-      </c>
       <c r="M45" s="5" t="n">
-        <v>67.2</v>
+        <v>0.21</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="O45" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3168,33 +3010,30 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.93</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="L46" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="M46" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O46" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3226,33 +3065,30 @@
         <v>0.87</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>56</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.9</v>
+        <v>89.2</v>
       </c>
       <c r="I47" s="5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K47" s="5" t="n">
         <v>0.99</v>
       </c>
-      <c r="J47" s="5" t="n">
+      <c r="L47" s="5" t="n">
         <v>0.97</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>3.67</v>
-      </c>
       <c r="M47" s="5" t="n">
-        <v>91.59999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="O47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3284,33 +3120,30 @@
         <v>0.76</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.84</v>
+        <v>84</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K48" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="L48" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="K48" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>1.38</v>
-      </c>
       <c r="M48" s="3" t="n">
-        <v>89</v>
+        <v>0.25</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O48" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P48" s="3" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3342,33 +3175,30 @@
         <v>0.74</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.84</v>
+        <v>82.3</v>
       </c>
       <c r="I49" s="5" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K49" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="J49" s="5" t="n">
+      <c r="L49" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>4.47</v>
-      </c>
       <c r="M49" s="5" t="n">
-        <v>83.09999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3400,33 +3230,30 @@
         <v>0.76</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.71</v>
+        <v>71</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.85</v>
+        <v>85.3</v>
       </c>
       <c r="I50" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K50" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="L50" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="K50" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>2.72</v>
-      </c>
       <c r="M50" s="3" t="n">
-        <v>83.2</v>
+        <v>0.44</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="O50" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P50" s="3" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3458,33 +3285,30 @@
         <v>0.66</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.92</v>
+        <v>92</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.44</v>
+        <v>50</v>
       </c>
       <c r="I51" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K51" s="5" t="n">
         <v>0.67</v>
       </c>
-      <c r="J51" s="5" t="n">
+      <c r="L51" s="5" t="n">
         <v>0.84</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>0.86</v>
-      </c>
       <c r="M51" s="5" t="n">
-        <v>50</v>
+        <v>0.19</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O51" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="P51" s="5" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3516,33 +3340,30 @@
         <v>0.76</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.74</v>
+        <v>74</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.98</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K52" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="L52" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="K52" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>2.97</v>
-      </c>
       <c r="M52" s="3" t="n">
-        <v>99</v>
+        <v>0.19</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O52" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P52" s="3" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3574,33 +3395,30 @@
         <v>0.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.62</v>
+        <v>60</v>
       </c>
       <c r="I53" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K53" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J53" s="5" t="n">
+      <c r="L53" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="M53" s="5" t="n">
-        <v>63.6</v>
+        <v>0.18</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P53" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3632,33 +3450,30 @@
         <v>0.71</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.6</v>
+        <v>58.4</v>
       </c>
       <c r="I54" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K54" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="L54" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="K54" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>3.99</v>
-      </c>
       <c r="M54" s="3" t="n">
-        <v>57.4</v>
+        <v>0.4</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O54" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P54" s="3" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3690,33 +3505,30 @@
         <v>0.72</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>79</v>
       </c>
       <c r="I55" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" s="5" t="n">
         <v>0.42</v>
       </c>
-      <c r="J55" s="5" t="n">
+      <c r="L55" s="5" t="n">
         <v>0.96</v>
       </c>
-      <c r="K55" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>1.69</v>
-      </c>
       <c r="M55" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O55" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3748,33 +3560,30 @@
         <v>0.6</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>81</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I56" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K56" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="L56" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K56" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="M56" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O56" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P56" s="3" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3806,33 +3615,30 @@
         <v>0.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.63</v>
+        <v>63</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I57" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K57" s="5" t="n">
         <v>0.39</v>
       </c>
-      <c r="J57" s="5" t="n">
+      <c r="L57" s="5" t="n">
         <v>0.92</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>3.07</v>
-      </c>
       <c r="M57" s="5" t="n">
-        <v>73.7</v>
+        <v>0.48</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="O57" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3864,33 +3670,30 @@
         <v>0.75</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.99</v>
+        <v>99</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.71</v>
+        <v>74.5</v>
       </c>
       <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K58" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="L58" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="K58" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M58" s="3" t="n">
-        <v>69.5</v>
+        <v>0.29</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O58" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3922,33 +3725,30 @@
         <v>0.65</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.79</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I59" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K59" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="J59" s="5" t="n">
+      <c r="L59" s="5" t="n">
         <v>0.83</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>3.53</v>
-      </c>
       <c r="M59" s="5" t="n">
-        <v>78.3</v>
+        <v>0.52</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="O59" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3980,33 +3780,30 @@
         <v>0.7</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.97</v>
+        <v>97</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.53</v>
+        <v>51.1</v>
       </c>
       <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K60" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="L60" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="K60" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" s="3" t="n">
-        <v>56.5</v>
+        <v>0.14</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O60" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P60" s="3" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4038,33 +3835,30 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.97</v>
+        <v>97</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I61" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K61" s="5" t="n">
         <v>0.58</v>
       </c>
-      <c r="J61" s="5" t="n">
+      <c r="L61" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>0.23</v>
-      </c>
       <c r="M61" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O61" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P61" s="5" t="inlineStr">
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4096,33 +3890,30 @@
         <v>0.71</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.6</v>
+        <v>59.9</v>
       </c>
       <c r="I62" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K62" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="L62" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="K62" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>1.2</v>
-      </c>
       <c r="M62" s="3" t="n">
-        <v>56.6</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O62" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4154,33 +3945,30 @@
         <v>0.71</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.64</v>
+        <v>60.7</v>
       </c>
       <c r="I63" s="5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K63" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="J63" s="5" t="n">
+      <c r="L63" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="K63" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>4.33</v>
-      </c>
       <c r="M63" s="5" t="n">
-        <v>68</v>
+        <v>0.35</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O63" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="O63" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4212,33 +4000,30 @@
         <v>0.71</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.59</v>
+        <v>59</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.62</v>
+        <v>64</v>
       </c>
       <c r="I64" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K64" s="3" t="n">
         <v>0.84</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="L64" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="K64" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="M64" s="3" t="n">
-        <v>62.1</v>
+        <v>0.43</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O64" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P64" s="3" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4270,33 +4055,30 @@
         <v>0.64</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.78</v>
+        <v>76</v>
       </c>
       <c r="I65" s="5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K65" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="J65" s="5" t="n">
+      <c r="L65" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>4.48</v>
-      </c>
       <c r="M65" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="O65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P65" s="5" t="inlineStr">
+      <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4328,33 +4110,30 @@
         <v>0.65</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.64</v>
+        <v>64</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I66" s="3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K66" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="L66" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="K66" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>2.89</v>
-      </c>
       <c r="M66" s="3" t="n">
-        <v>68.2</v>
+        <v>0.63</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="O66" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P66" s="3" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4386,33 +4165,30 @@
         <v>0.75</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.92</v>
+        <v>92</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I67" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K67" s="5" t="n">
         <v>0.43</v>
       </c>
-      <c r="J67" s="5" t="n">
+      <c r="L67" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>1.21</v>
-      </c>
       <c r="M67" s="5" t="n">
-        <v>83.7</v>
+        <v>0.47</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="O67" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P67" s="5" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4444,33 +4220,30 @@
         <v>0.75</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.67</v>
+        <v>67</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.67</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I68" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K68" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="L68" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="K68" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>2.78</v>
-      </c>
       <c r="M68" s="3" t="n">
-        <v>68.2</v>
+        <v>0.45</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O68" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P68" s="3" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4502,33 +4275,30 @@
         <v>0.6</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.93</v>
+        <v>93</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.41</v>
+        <v>50</v>
       </c>
       <c r="I69" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="K69" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="J69" s="5" t="n">
+      <c r="L69" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0.64</v>
-      </c>
       <c r="M69" s="5" t="n">
-        <v>50</v>
+        <v>0.23</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O69" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P69" s="5" t="inlineStr">
+      <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4560,33 +4330,30 @@
         <v>0.75</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.9</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I70" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="K70" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="L70" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="K70" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>2.47</v>
-      </c>
       <c r="M70" s="3" t="n">
-        <v>91</v>
+        <v>0.08</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O70" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P70" s="3" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4618,33 +4385,30 @@
         <v>0.74</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="H71" s="5" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L71" s="5" t="n">
         <v>0.83</v>
       </c>
-      <c r="I71" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>4.48</v>
-      </c>
       <c r="M71" s="5" t="n">
-        <v>82</v>
+        <v>0.38</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O71" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P71" s="5" t="inlineStr">
+      <c r="O71" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4676,33 +4440,30 @@
         <v>0.7</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.76</v>
+        <v>76</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.78</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I72" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K72" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="L72" s="3" t="n">
         <v>0.62</v>
       </c>
-      <c r="K72" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>1.64</v>
-      </c>
       <c r="M72" s="3" t="n">
-        <v>76.2</v>
+        <v>0.17</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="O72" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P72" s="3" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4734,33 +4495,30 @@
         <v>0.66</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.44</v>
+        <v>50</v>
       </c>
       <c r="I73" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="K73" s="5" t="n">
         <v>0.61</v>
       </c>
-      <c r="J73" s="5" t="n">
+      <c r="L73" s="5" t="n">
         <v>0.84</v>
       </c>
-      <c r="K73" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>1.54</v>
-      </c>
       <c r="M73" s="5" t="n">
-        <v>50</v>
+        <v>0.16</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O73" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P73" s="5" t="inlineStr">
+      <c r="O73" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4792,33 +4550,30 @@
         <v>0.8</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.83</v>
+        <v>83</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.92</v>
+        <v>93</v>
       </c>
       <c r="I74" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K74" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="L74" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K74" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="M74" s="3" t="n">
-        <v>90.8</v>
+        <v>0.2</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O74" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P74" s="3" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4850,33 +4605,30 @@
         <v>0.64</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>81</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.62</v>
+        <v>60.9</v>
       </c>
       <c r="I75" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K75" s="5" t="n">
         <v>0.41</v>
       </c>
-      <c r="J75" s="5" t="n">
+      <c r="L75" s="5" t="n">
         <v>0.66</v>
       </c>
-      <c r="K75" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M75" s="5" t="n">
-        <v>62.4</v>
+        <v>0.11</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O75" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P75" s="5" t="inlineStr">
+      <c r="O75" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4908,33 +4660,30 @@
         <v>0.64</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.98</v>
+        <v>98</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.65</v>
+        <v>65.3</v>
       </c>
       <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K76" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="L76" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="K76" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M76" s="3" t="n">
-        <v>65.2</v>
+        <v>0.1</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P76" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4966,33 +4715,30 @@
         <v>0.75</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.55</v>
+        <v>55</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.91</v>
+        <v>90</v>
       </c>
       <c r="I77" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K77" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="J77" s="5" t="n">
+      <c r="L77" s="5" t="n">
         <v>0.64</v>
       </c>
-      <c r="K77" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>3.89</v>
-      </c>
       <c r="M77" s="5" t="n">
-        <v>91</v>
+        <v>0.32</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="O77" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="P77" s="5" t="inlineStr">
+      <c r="O77" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5024,33 +4770,30 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.99</v>
+        <v>99</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.59</v>
+        <v>59.7</v>
       </c>
       <c r="I78" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K78" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="L78" s="3" t="n">
         <v>0.68</v>
       </c>
-      <c r="K78" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0.39</v>
-      </c>
       <c r="M78" s="3" t="n">
-        <v>62.1</v>
+        <v>0.14</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O78" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P78" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5082,33 +4825,30 @@
         <v>0.74</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.75</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I79" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K79" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="J79" s="5" t="n">
+      <c r="L79" s="5" t="n">
         <v>0.86</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>1.71</v>
-      </c>
       <c r="M79" s="5" t="n">
-        <v>75.7</v>
+        <v>0.22</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="O79" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="P79" s="5" t="inlineStr">
+      <c r="O79" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5140,33 +4880,30 @@
         <v>0.63</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.57</v>
+        <v>57</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="I80" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K80" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="L80" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="K80" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>3.73</v>
-      </c>
       <c r="M80" s="3" t="n">
-        <v>82.2</v>
+        <v>0.23</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O80" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P80" s="3" t="inlineStr">
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5198,33 +4935,30 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.86</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I81" s="5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K81" s="5" t="n">
         <v>0.43</v>
       </c>
-      <c r="J81" s="5" t="n">
+      <c r="L81" s="5" t="n">
         <v>0.95</v>
       </c>
-      <c r="K81" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>2.24</v>
-      </c>
       <c r="M81" s="5" t="n">
-        <v>86.3</v>
+        <v>0.2</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O81" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P81" s="5" t="inlineStr">
+      <c r="O81" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5256,33 +4990,30 @@
         <v>0.52</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.74</v>
+        <v>74</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.45</v>
+        <v>50</v>
       </c>
       <c r="I82" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K82" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="L82" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K82" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>2.68</v>
-      </c>
       <c r="M82" s="3" t="n">
-        <v>50</v>
+        <v>0.32</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="O82" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P82" s="3" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5314,33 +5045,30 @@
         <v>0.8</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.62</v>
+        <v>57.6</v>
       </c>
       <c r="I83" s="5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K83" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="5" t="n">
+      <c r="L83" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>4.33</v>
-      </c>
       <c r="M83" s="5" t="n">
-        <v>64.59999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O83" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P83" s="5" t="inlineStr">
+      <c r="O83" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5372,33 +5100,30 @@
         <v>0.64</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>69</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.64</v>
+        <v>61.5</v>
       </c>
       <c r="I84" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K84" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="L84" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="K84" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>3.07</v>
-      </c>
       <c r="M84" s="3" t="n">
-        <v>63.8</v>
+        <v>0.4</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O84" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P84" s="3" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5430,33 +5155,30 @@
         <v>0.79</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.96</v>
+        <v>96</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="I85" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K85" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="J85" s="5" t="n">
+      <c r="L85" s="5" t="n">
         <v>0.93</v>
       </c>
-      <c r="K85" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>0.4</v>
-      </c>
       <c r="M85" s="5" t="n">
-        <v>51.4</v>
+        <v>0.15</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O85" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P85" s="5" t="inlineStr">
+      <c r="O85" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5488,33 +5210,30 @@
         <v>0.6</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H86" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M86" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="I86" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="N86" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="O86" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P86" s="3" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5546,33 +5265,30 @@
         <v>0.55</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.62</v>
+        <v>62</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0.58</v>
+        <v>53.2</v>
       </c>
       <c r="I87" s="5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K87" s="5" t="n">
         <v>0.41</v>
       </c>
-      <c r="J87" s="5" t="n">
+      <c r="L87" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>2.94</v>
-      </c>
       <c r="M87" s="5" t="n">
-        <v>57.9</v>
+        <v>0.39</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="O87" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P87" s="5" t="inlineStr">
+      <c r="O87" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5604,33 +5320,30 @@
         <v>0.62</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.86</v>
+        <v>86</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.53</v>
+        <v>53.4</v>
       </c>
       <c r="I88" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K88" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="L88" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K88" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0.58</v>
-      </c>
       <c r="M88" s="3" t="n">
-        <v>52.5</v>
+        <v>0.18</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O88" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P88" s="3" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5662,33 +5375,30 @@
         <v>0.63</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.98</v>
+        <v>98</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.57</v>
+        <v>55.5</v>
       </c>
       <c r="I89" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K89" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="J89" s="5" t="n">
+      <c r="L89" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>0.25</v>
-      </c>
       <c r="M89" s="5" t="n">
-        <v>55.4</v>
+        <v>0.49</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="O89" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P89" s="5" t="inlineStr">
+      <c r="O89" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5720,33 +5430,30 @@
         <v>0.77</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.91</v>
+        <v>91</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.65</v>
+        <v>65.2</v>
       </c>
       <c r="I90" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K90" s="3" t="n">
         <v>0.63</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="L90" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="K90" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>1.05</v>
-      </c>
       <c r="M90" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O90" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P90" s="3" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5778,33 +5485,30 @@
         <v>0.61</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.58</v>
+        <v>58.4</v>
       </c>
       <c r="I91" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K91" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="J91" s="5" t="n">
+      <c r="L91" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="K91" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>3.77</v>
-      </c>
       <c r="M91" s="5" t="n">
-        <v>56.9</v>
+        <v>0.26</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="O91" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P91" s="5" t="inlineStr">
+      <c r="O91" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5836,33 +5540,30 @@
         <v>0.88</v>
       </c>
       <c r="G92" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K92" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="H92" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J92" s="3" t="n">
+      <c r="L92" s="3" t="n">
         <v>0.91</v>
       </c>
-      <c r="K92" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M92" s="3" t="n">
-        <v>77.8</v>
+        <v>0.61</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O92" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P92" s="3" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5894,33 +5595,30 @@
         <v>0.78</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.72</v>
+        <v>70.2</v>
       </c>
       <c r="I93" s="5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K93" s="5" t="n">
         <v>0.88</v>
       </c>
-      <c r="J93" s="5" t="n">
+      <c r="L93" s="5" t="n">
         <v>0.76</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>3.28</v>
-      </c>
       <c r="M93" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O93" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="O93" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5952,33 +5650,30 @@
         <v>0.62</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.67</v>
+        <v>68</v>
       </c>
       <c r="I94" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K94" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="J94" s="3" t="n">
+      <c r="L94" s="3" t="n">
         <v>0.61</v>
       </c>
-      <c r="K94" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>2.03</v>
-      </c>
       <c r="M94" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O94" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P94" s="3" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6010,33 +5705,30 @@
         <v>0.7</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.92</v>
+        <v>92</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.79</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I95" s="5" t="n">
         <v>0.33</v>
       </c>
       <c r="J95" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L95" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="K95" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L95" s="5" t="n">
+      <c r="M95" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="M95" s="5" t="n">
-        <v>79.59999999999999</v>
-      </c>
       <c r="N95" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O95" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P95" s="5" t="inlineStr">
+      <c r="O95" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6068,33 +5760,30 @@
         <v>0.6</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.57</v>
+        <v>57</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.82</v>
+        <v>82.2</v>
       </c>
       <c r="I96" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K96" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J96" s="3" t="n">
+      <c r="L96" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="K96" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>3.27</v>
-      </c>
       <c r="M96" s="3" t="n">
-        <v>84</v>
+        <v>0.15</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O96" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P96" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6126,33 +5815,30 @@
         <v>0.74</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.73</v>
+        <v>70.2</v>
       </c>
       <c r="I97" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K97" s="5" t="n">
         <v>0.68</v>
       </c>
-      <c r="J97" s="5" t="n">
+      <c r="L97" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>2.38</v>
-      </c>
       <c r="M97" s="5" t="n">
-        <v>75.40000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="O97" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P97" s="5" t="inlineStr">
+      <c r="O97" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6184,33 +5870,30 @@
         <v>0.83</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0.89</v>
+        <v>89</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I98" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K98" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="J98" s="3" t="n">
+      <c r="L98" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="K98" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>0.73</v>
-      </c>
       <c r="M98" s="3" t="n">
-        <v>94.7</v>
+        <v>0.12</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O98" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P98" s="3" t="inlineStr">
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6242,33 +5925,30 @@
         <v>0.67</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.68</v>
+        <v>68</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.46</v>
+        <v>50</v>
       </c>
       <c r="I99" s="5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K99" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="J99" s="5" t="n">
+      <c r="L99" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="K99" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>2.76</v>
-      </c>
       <c r="M99" s="5" t="n">
-        <v>50</v>
+        <v>0.17</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="O99" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P99" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6300,33 +5980,30 @@
         <v>0.54</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.55</v>
+        <v>55</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0.58</v>
+        <v>60.2</v>
       </c>
       <c r="I100" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K100" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="J100" s="3" t="n">
+      <c r="L100" s="3" t="n">
         <v>0.88</v>
       </c>
-      <c r="K100" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>3.51</v>
-      </c>
       <c r="M100" s="3" t="n">
-        <v>59.2</v>
+        <v>0.11</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O100" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="P100" s="3" t="inlineStr">
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6358,429 +6035,32 @@
         <v>0.88</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.87</v>
+        <v>85.7</v>
       </c>
       <c r="I101" s="5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K101" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J101" s="5" t="n">
+      <c r="L101" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="K101" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>2.36</v>
-      </c>
       <c r="M101" s="5" t="n">
-        <v>89.09999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O101" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P101" s="5" t="inlineStr">
+      <c r="O101" s="4" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Column Name</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Range / Values</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>supplier_name</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Unique supplier company name</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Country of primary operations</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>e.g. China, USA, Germany</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Procurement spend category</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>e.g. Electronics, Automotive</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Supply chain tier level</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>1 = Strategic, 2 = Preferred, 3 = Transactional</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>annual_spend</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Annual procurement spend in USD</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>$50K – $150M</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>risk_score</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Overall risk index (MCDM-based)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>0.0 – 1.0 (higher = more risk)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>quality_score</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Quality compliance score</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>0.0 – 1.0 (higher = better)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>delivery_performance</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>On-time delivery performance</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>0.0 – 1.0 (higher = better)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>financial_stability</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Financial health score</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>0.0 – 1.0 (higher = more stable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>compliance_score</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Regulatory adherence score</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>0.0 – 1.0 (higher = more compliant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>lead_time_days</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Average lead time in days</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>3 – 90 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>defect_rate</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Defect rate percentage</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>0.0 – 15.0 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>on_time_delivery</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>On-time delivery percentage</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>50.0 – 100.0 (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>dependency_score</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Sole-source dependency risk</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>0.0 – 1.0 (higher = more dependent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>sub_tier_count</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Number of sub-tier (Tier-2) suppliers</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>1 – 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>criticality</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Risk classification</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
         </is>
       </c>
     </row>
